--- a/for_reference/outputs/TASK_A_B_EVALUATE_EXECUTE.xlsx
+++ b/for_reference/outputs/TASK_A_B_EVALUATE_EXECUTE.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RA should-have-been" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,10 +476,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -490,10 +491,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>evaluate-execute is a multi-turn ReAct judge (unlike evaluate-interpret's single-shot call): it actively inspects the study's Docker specs, file system, and execution logs via tool calls, rather than comparing self-reported text to a reference document. 10 reference-free binary (0/1) checkpoints, no comparison to a human reference. Task A's run is from the original PR #12 submission; Task B's run was executed for the first time to build this comparison.</t>
+          <t>evaluate-execute is a multi-turn ReAct judge (unlike evaluate-interpret's single-shot call): it actively inspects the study's Docker specs, file system, and execution logs via tool calls, rather than comparing self-reported text to a reference document. 10 reference-free binary (0/1) checkpoints, no comparison to a human reference. Task A's run is from the original PR #12 submission; Task B's run was executed for the first time to build this comparison. "RA should-have-been" is a FABRICATED execution_results.json (RA's own real Docker specs/logs/output files, unchanged) that honestly flags the spike-and-collapse anomaly instead of claiming success, to test whether the checkpoints react to honesty about wrong results.</t>
         </is>
       </c>
     </row>
@@ -541,6 +542,21 @@
       </c>
       <c r="C6" s="6">
         <f>'Codex'!B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>RA should-have-been (fabricated, honest)</t>
+        </is>
+      </c>
+      <c r="B7" s="5">
+        <f>'RA should-have-been'!B14</f>
+        <v/>
+      </c>
+      <c r="C7" s="6">
+        <f>'RA should-have-been'!B15</f>
         <v/>
       </c>
     </row>
@@ -991,4 +1007,224 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>evaluate-execute run: Task A (RA), FABRICATED honest execution_results.json (evaluator_model=gpt-4o)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Checkpoint</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Score (0/1)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Judge's explanation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.1.1 -- Verify that docker_specs.base_image exists</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>The Dockerfile specifies 'python:3.10-slim' as the base image, confirming its presence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>1.1.2 -- Check for missing manifest</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Though a manifest or installation process is implied through the Dockerfile, no explicit manifest file was observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>1.2 -- Agent successfully identifies imports/libraries and reports them under docker_specs.packages</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Dependencies like 'numpy' and 'matplotlib' were correctly identified and included in the 'docker_specs.packages'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>1.3.1 -- Agent detects and fixes all hard-coded paths</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>The script uses dynamic paths for outputs, reflecting a robust design without hardcoding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>1.3.2 -- replication_info.codebase.files exist in folder</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>The file 'scarcity_of_labor_replication__py.py' is present in the specified folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>1.3.3 -- If there is data to be mounted, it has the correct path</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>The data to be mounted is correctly set up in Docker using './data:/app/data' path specification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2.1.1 -- Data is successfully loaded</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Data and scripts are loaded successfully as indicated by the absence of errors during execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>2.2.2 -- Main code/model is executed without errors</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>The main model and code executed successfully without errors inside the Docker container.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2.3.1 -- Expected output files generated by code, if any, are logged and reported</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Output files are generated, logged, and stored as .npz and JSON, including visual plots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2.3.2 -- JSON report is filled out</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>The 'execution_results.json' is filled out, summarizing the process and discrepancies in output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>SUM(B4:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>B14/10</f>
+        <v/>
+      </c>
+      <c r="C15" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>